--- a/data/trans_orig/IP3109_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_2023-Estudios-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>9823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18439</t>
+          <t>16863</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25975</t>
+          <t>27143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26304</t>
+          <t>27256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>10661</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35612</t>
+          <t>34136</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>20715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38934</t>
+          <t>38820</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>31324</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43679</t>
+          <t>44910</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56418</t>
+          <t>55867</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79050</t>
+          <t>78933</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>12213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23501</t>
+          <t>25658</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>20371</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39090</t>
+          <t>38701</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51603</t>
+          <t>51480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45707</t>
+          <t>46929</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72274</t>
+          <t>73257</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81898</t>
+          <t>81281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118031</t>
+          <t>116133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62731</t>
+          <t>63788</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93517</t>
+          <t>95024</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>91964</t>
+          <t>90942</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>130857</t>
+          <t>132692</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>165484</t>
+          <t>166712</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>217237</t>
+          <t>217860</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>294264</t>
+          <t>293594</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>341111</t>
+          <t>337986</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>296057</t>
+          <t>295074</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>340856</t>
+          <t>342054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>602382</t>
+          <t>599946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>667894</t>
+          <t>666996</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,75%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>578</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>9196</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21311</t>
+          <t>21677</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>22346</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>21292</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39555</t>
+          <t>39947</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19985</t>
+          <t>20086</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35198</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24983</t>
+          <t>25508</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45166</t>
+          <t>43640</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48659</t>
+          <t>48372</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74074</t>
+          <t>73086</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88630</t>
+          <t>88473</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>107322</t>
+          <t>107043</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>113268</t>
+          <t>113820</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>136735</t>
+          <t>136434</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>207092</t>
+          <t>208732</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>237436</t>
+          <t>238272</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11658</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>18127</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>922</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30176</t>
+          <t>30237</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30776</t>
+          <t>31954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>32643</t>
+          <t>33308</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>55031</t>
+          <t>55985</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49122</t>
+          <t>48855</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>76092</t>
+          <t>76992</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69808</t>
+          <t>69128</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>102535</t>
+          <t>100865</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>127607</t>
+          <t>126098</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>166575</t>
+          <t>166920</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>99607</t>
+          <t>100983</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>141049</t>
+          <t>142728</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>126840</t>
+          <t>127036</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>174211</t>
+          <t>171494</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>238151</t>
+          <t>237573</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>298271</t>
+          <t>300068</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>417666</t>
+          <t>416785</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>471124</t>
+          <t>470562</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>453867</t>
+          <t>456600</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>508176</t>
+          <t>509139</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>890651</t>
+          <t>887230</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>971541</t>
+          <t>963136</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3109_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1477</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4512</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4852</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5159</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1477</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4617</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3693</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1499</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8546</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,06%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>849</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4626</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3415</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4072</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1678</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8774</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9073</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4783</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15383</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,05%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7235</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3683</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13023</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13,47%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16863</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18059</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>10829</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27143</t>
+          <t>23229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2153</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10097</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12924</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6375</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27256</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>24,07%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,87%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>50,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>18150</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34136</t>
+          <t>20153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>35362</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>28623</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40796</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>66,47%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>53,8%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>76,68%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31213</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>20715</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>38820</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>58,13%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>38,58%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>72,29%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37659</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31324</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44910</t>
+          <t>33368</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>68871</t>
+          <t>63250</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>55867</t>
+          <t>54325</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>78933</t>
+          <t>71282</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53203</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>53203</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>53203</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>45905</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>45905</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>45905</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>57780</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>57780</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>57780</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>143</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>111478</t>
+          <t>99108</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111478</t>
+          <t>99108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111478</t>
+          <t>99108</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3892</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10237</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2254</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6153</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>356</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5267</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3373</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2321</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1087</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>4975</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>358</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11119</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6282</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18151</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15922</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10539</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25658</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20412</t>
+          <t>23940</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>28428</t>
+          <t>26454</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20371</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38701</t>
+          <t>36213</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51251</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>41037</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>63438</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10,99%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>39852</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>29779</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>51480</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>59207</t>
+          <t>39692</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46929</t>
+          <t>31157</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73257</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>99059</t>
+          <t>90942</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81281</t>
+          <t>75925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116133</t>
+          <t>106635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>105267</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>88459</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>126520</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>22,57%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>18,97%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>27,13%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>79329</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>63788</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>95024</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>14,14%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>21,07%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>110095</t>
+          <t>82086</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>90942</t>
+          <t>68047</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>132692</t>
+          <t>96068</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>189425</t>
+          <t>187354</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>166712</t>
+          <t>166903</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>217860</t>
+          <t>212002</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>293579</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>272607</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>313701</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>62,94%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>58,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,26%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>411</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>313106</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>293594</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>337986</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>69,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,1%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74,94%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>318959</t>
+          <t>283655</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>295074</t>
+          <t>267475</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>342054</t>
+          <t>301111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>632066</t>
+          <t>577234</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>599946</t>
+          <t>551180</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>666996</t>
+          <t>602594</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>624</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>451007</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>451007</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>451007</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>423793</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>423793</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>423793</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>505250</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>505250</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>505250</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1254</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>956258</t>
+          <t>890216</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>956258</t>
+          <t>890216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>956258</t>
+          <t>890216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5912</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5722</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1928</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7550</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>477</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -2423,107 +2423,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5625</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4454</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5178</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5089</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,67 +2576,67 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>9127</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>6,2%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>9543</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>5170</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>15771</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>9826</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>5356</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>16575</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -2654,69 +2654,69 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21677</t>
+          <t>19274</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>14814</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>9577</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>21828</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>10,07%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
           <t>14,83%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>14468</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>8645</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>22346</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>42</t>
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>28951</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21292</t>
+          <t>19493</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39947</t>
+          <t>35431</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>32275</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>24221</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>41945</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>25,16%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>26879</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>20086</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>35152</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>18,39%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>24,05%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>33676</t>
+          <t>26702</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>19963</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43640</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>60555</t>
+          <t>58977</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48372</t>
+          <t>48367</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73086</t>
+          <t>72565</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>115590</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>104494</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>125018</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>69,35%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>62,69%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>75,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>97820</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>88473</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>107043</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>66,91%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>60,52%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>73,22%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>125561</t>
+          <t>98479</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>113820</t>
+          <t>89499</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>136434</t>
+          <t>107579</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>223381</t>
+          <t>214069</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>208732</t>
+          <t>197874</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>238272</t>
+          <t>227552</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,51%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>147140</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>147140</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>147140</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>181139</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>181139</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>181139</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>455</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3218,107 +3218,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5763</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>6195</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5503</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>3343</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>7466</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1087</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>6323</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>3157</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>7806</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>29590</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>22083</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>31954</t>
+          <t>29851</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>43175</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>31056</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>55985</t>
+          <t>52434</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>72427</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>58950</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>85228</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>61570</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>48855</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>76992</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>84499</t>
+          <t>61717</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69128</t>
+          <t>50847</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>100865</t>
+          <t>76089</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>146069</t>
+          <t>134144</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>126098</t>
+          <t>117530</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>166920</t>
+          <t>156422</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>142618</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>123591</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>162800</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>20,78%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>18,01%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>23,72%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>119132</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>100983</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>142728</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>18,3%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>15,51%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>21,93%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>148997</t>
+          <t>116980</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>127036</t>
+          <t>101108</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>171494</t>
+          <t>134716</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>268130</t>
+          <t>259598</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>237573</t>
+          <t>235367</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>300068</t>
+          <t>286710</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>444531</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>422107</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>466943</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>64,77%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>61,5%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>68,04%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>442139</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>416785</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>470562</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>67,93%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>64,03%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>72,29%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>482179</t>
+          <t>410022</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>456600</t>
+          <t>388943</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>509139</t>
+          <t>428431</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>924319</t>
+          <t>854553</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>887230</t>
+          <t>823670</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>963136</t>
+          <t>882703</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>67,74%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>913</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>650892</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>650892</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>650892</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>616837</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>616837</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>616837</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>744169</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>744169</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>744169</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>1852</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1395061</t>
+          <t>1303149</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1395061</t>
+          <t>1303149</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1395061</t>
+          <t>1303149</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
